--- a/Eval_results/District_stats/district_own/summary.xlsx
+++ b/Eval_results/District_stats/district_own/summary.xlsx
@@ -476,29 +476,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>丰台区</t>
+          <t>Fengtai</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-5.247531421482563</v>
+        <v>-5.247529767453671</v>
       </c>
       <c r="D2" t="n">
-        <v>54.7673846706748</v>
+        <v>54.7675790861249</v>
       </c>
       <c r="E2" t="n">
-        <v>2.087764739990234</v>
+        <v>27.42986679077148</v>
       </c>
       <c r="F2" t="n">
-        <v>51.60761798918247</v>
+        <v>76.94991610944271</v>
       </c>
       <c r="G2" t="n">
-        <v>-5247531421.482563</v>
+        <v>-5247529767.453671</v>
       </c>
       <c r="H2" t="n">
-        <v>54.7673846706748</v>
+        <v>54.7675790861249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002982521057128906</v>
+        <v>0.03918552398681641</v>
       </c>
     </row>
     <row r="3">
@@ -507,29 +507,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>剩余五区</t>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.20619548857212</v>
+        <v>15.20619411766529</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.251269668340683</v>
+        <v>-3.251269653439522</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04294713458511978</v>
+        <v>-21.09661102294922</v>
       </c>
       <c r="F3" t="n">
-        <v>11.99787295481656</v>
+        <v>-9.14168655872345</v>
       </c>
       <c r="G3" t="n">
-        <v>15206195488.57212</v>
+        <v>15206194117.66529</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.251269668340683</v>
+        <v>-3.251269653439522</v>
       </c>
       <c r="I3" t="n">
-        <v>6.135304940731398e-05</v>
+        <v>-0.03013801574707031</v>
       </c>
     </row>
     <row r="4">
@@ -538,29 +538,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>大兴区</t>
+          <t>Daxing</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.87183521315455</v>
+        <v>10.87183353677392</v>
       </c>
       <c r="D4" t="n">
-        <v>9.445833530277014</v>
+        <v>9.445800986140966</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4052607414778322</v>
+        <v>-0.4602909088134766</v>
       </c>
       <c r="F4" t="n">
-        <v>20.7229294849094</v>
+        <v>19.85734361410141</v>
       </c>
       <c r="G4" t="n">
-        <v>10871835213.15455</v>
+        <v>10871833536.77392</v>
       </c>
       <c r="H4" t="n">
-        <v>9.445833530277014</v>
+        <v>9.445800986140966</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005789439163969032</v>
+        <v>-0.0006575584411621094</v>
       </c>
     </row>
     <row r="5">
@@ -569,29 +569,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>房山区</t>
+          <t>Fangshan</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-15.01395744457841</v>
+        <v>-15.01395829766989</v>
       </c>
       <c r="D5" t="n">
-        <v>37.63274896144867</v>
+        <v>37.6327166557312</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4373041851213202</v>
+        <v>119.3578720092773</v>
       </c>
       <c r="F5" t="n">
-        <v>23.05609570199158</v>
+        <v>141.9766303673387</v>
       </c>
       <c r="G5" t="n">
-        <v>-15013957444.57841</v>
+        <v>-15013958297.66989</v>
       </c>
       <c r="H5" t="n">
-        <v>37.63274896144867</v>
+        <v>37.6327166557312</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006247202644590288</v>
+        <v>0.1705112457275391</v>
       </c>
     </row>
     <row r="6">
@@ -600,29 +600,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>昌平区</t>
+          <t>Changping</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.146921159699559</v>
+        <v>8.146920496597886</v>
       </c>
       <c r="D6" t="n">
-        <v>77.33125400543213</v>
+        <v>77.33118915557861</v>
       </c>
       <c r="E6" t="n">
-        <v>1.820424444973469</v>
+        <v>97.25522994995117</v>
       </c>
       <c r="F6" t="n">
-        <v>87.29859961010516</v>
+        <v>182.7333396021277</v>
       </c>
       <c r="G6" t="n">
-        <v>8146921159.699558</v>
+        <v>8146920496.597885</v>
       </c>
       <c r="H6" t="n">
-        <v>77.33125400543213</v>
+        <v>77.33118915557861</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002600606349962098</v>
+        <v>0.1389360427856445</v>
       </c>
     </row>
     <row r="7">
@@ -631,29 +631,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>朝阳区</t>
+          <t>Chaoyang</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.57236433029175</v>
+        <v>48.5723625421524</v>
       </c>
       <c r="D7" t="n">
-        <v>18.03281301259995</v>
+        <v>18.03261762857437</v>
       </c>
       <c r="E7" t="n">
-        <v>2.822628021240234</v>
+        <v>23.55461120605469</v>
       </c>
       <c r="F7" t="n">
-        <v>69.42780536413193</v>
+        <v>90.15959137678146</v>
       </c>
       <c r="G7" t="n">
-        <v>48572364330.29175</v>
+        <v>48572362542.1524</v>
       </c>
       <c r="H7" t="n">
-        <v>18.03281301259995</v>
+        <v>18.03261762857437</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004032325744628906</v>
+        <v>0.03364944458007812</v>
       </c>
     </row>
     <row r="8">
@@ -662,29 +662,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>海淀区</t>
+          <t>Haidian</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40.59718391299248</v>
+        <v>40.59718304872513</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3509115725755692</v>
+        <v>0.351074680685997</v>
       </c>
       <c r="E8" t="n">
-        <v>1.725896148011088</v>
+        <v>-9.28492546081543</v>
       </c>
       <c r="F8" t="n">
-        <v>42.67399163357913</v>
+        <v>31.6633322685957</v>
       </c>
       <c r="G8" t="n">
-        <v>40597183912.99248</v>
+        <v>40597183048.72513</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3509115725755692</v>
+        <v>0.351074680685997</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002465565925730126</v>
+        <v>-0.01326417922973633</v>
       </c>
     </row>
     <row r="9">
@@ -693,29 +693,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>通州区</t>
+          <t>Tongzhou</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>95.46203278005123</v>
+        <v>95.46202316880226</v>
       </c>
       <c r="D9" t="n">
-        <v>-19.99169987998903</v>
+        <v>-19.99163490347564</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6050427947193384</v>
+        <v>-112.2322044372559</v>
       </c>
       <c r="F9" t="n">
-        <v>76.07537569478154</v>
+        <v>-36.76181617192924</v>
       </c>
       <c r="G9" t="n">
-        <v>95462032780.05122</v>
+        <v>95462023168.80226</v>
       </c>
       <c r="H9" t="n">
-        <v>-19.99169987998903</v>
+        <v>-19.99163490347564</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0008643468495990548</v>
+        <v>-0.1603317206246512</v>
       </c>
     </row>
     <row r="10">
@@ -724,29 +724,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>顺义区</t>
+          <t>Shunyi</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>43.175213329494</v>
+        <v>43.17520288378</v>
       </c>
       <c r="D10" t="n">
-        <v>18.2650564648211</v>
+        <v>18.26501560583711</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1030731271021068</v>
+        <v>911.5589179992676</v>
       </c>
       <c r="F10" t="n">
-        <v>61.54334292141721</v>
+        <v>972.9991364888847</v>
       </c>
       <c r="G10" t="n">
-        <v>43175213329.494</v>
+        <v>43175202883.78</v>
       </c>
       <c r="H10" t="n">
-        <v>18.2650564648211</v>
+        <v>18.26501560583711</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001472473244315812</v>
+        <v>1.302227025713239</v>
       </c>
     </row>
   </sheetData>
